--- a/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
+++ b/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
+++ b/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
+++ b/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
+++ b/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
+++ b/branches/Richard/ValueSet-vs-patient-consent-for-sms-notifications.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
